--- a/Roguelike-Deckbuilder/Assets/Config/Excel/ShopConfig.xlsx
+++ b/Roguelike-Deckbuilder/Assets/Config/Excel/ShopConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GIT\Unity-Roguelike-Deckbuilder\Roguelike-Deckbuilder\Assets\Config\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{883501C3-BE92-4B71-BDD1-E8ECBF516C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E9DFB82-CD1C-4A13-AA49-787B2FE128CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -620,7 +620,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.6640625" customWidth="1"/>
@@ -698,11 +698,246 @@
         <v>1</v>
       </c>
       <c r="D4" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E4" s="1">
         <v>50</v>
       </c>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+      <c r="C5" s="1">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1">
+        <v>50</v>
+      </c>
+      <c r="E5" s="1">
+        <v>50</v>
+      </c>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>3</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>5</v>
+      </c>
+      <c r="D6" s="1">
+        <v>30</v>
+      </c>
+      <c r="E6" s="1">
+        <v>50</v>
+      </c>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>4</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>7</v>
+      </c>
+      <c r="D7" s="1">
+        <v>30</v>
+      </c>
+      <c r="E7" s="1">
+        <v>50</v>
+      </c>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>5</v>
+      </c>
+      <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1">
+        <v>9</v>
+      </c>
+      <c r="D8" s="1">
+        <v>10</v>
+      </c>
+      <c r="E8" s="1">
+        <v>50</v>
+      </c>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1">
+        <v>2</v>
+      </c>
+      <c r="C9" s="1">
+        <v>1</v>
+      </c>
+      <c r="D9" s="1">
+        <v>50</v>
+      </c>
+      <c r="E9" s="1">
+        <v>150</v>
+      </c>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1">
+        <v>2</v>
+      </c>
+      <c r="C10" s="1">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1">
+        <v>50</v>
+      </c>
+      <c r="E10" s="1">
+        <v>150</v>
+      </c>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>8</v>
+      </c>
+      <c r="B11" s="1">
+        <v>2</v>
+      </c>
+      <c r="C11" s="1">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1">
+        <v>30</v>
+      </c>
+      <c r="E11" s="1">
+        <v>150</v>
+      </c>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>9</v>
+      </c>
+      <c r="B12" s="1">
+        <v>2</v>
+      </c>
+      <c r="C12" s="1">
+        <v>4</v>
+      </c>
+      <c r="D12" s="1">
+        <v>30</v>
+      </c>
+      <c r="E12" s="1">
+        <v>150</v>
+      </c>
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>10</v>
+      </c>
+      <c r="B13" s="1">
+        <v>2</v>
+      </c>
+      <c r="C13" s="1">
+        <v>5</v>
+      </c>
+      <c r="D13" s="1">
+        <v>10</v>
+      </c>
+      <c r="E13" s="1">
+        <v>150</v>
+      </c>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>11</v>
+      </c>
+      <c r="B14" s="1">
+        <v>2</v>
+      </c>
+      <c r="C14" s="1">
+        <v>6</v>
+      </c>
+      <c r="D14" s="1">
+        <v>10</v>
+      </c>
+      <c r="E14" s="1">
+        <v>150</v>
+      </c>
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>12</v>
+      </c>
+      <c r="B15" s="1">
+        <v>2</v>
+      </c>
+      <c r="C15" s="1">
+        <v>7</v>
+      </c>
+      <c r="D15" s="1">
+        <v>10</v>
+      </c>
+      <c r="E15" s="1">
+        <v>150</v>
+      </c>
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>13</v>
+      </c>
+      <c r="B16" s="1">
+        <v>2</v>
+      </c>
+      <c r="C16" s="1">
+        <v>8</v>
+      </c>
+      <c r="D16" s="1">
+        <v>10</v>
+      </c>
+      <c r="E16" s="1">
+        <v>150</v>
+      </c>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>14</v>
+      </c>
+      <c r="B17" s="1">
+        <v>2</v>
+      </c>
+      <c r="C17" s="1">
+        <v>9</v>
+      </c>
+      <c r="D17" s="1">
+        <v>10</v>
+      </c>
+      <c r="E17" s="1">
+        <v>150</v>
+      </c>
+      <c r="F17" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
